--- a/VerveStacks_BIH_grids_kan10/vt_vervestacks_BIH_v1.xlsx
+++ b/VerveStacks_BIH_grids_kan10/vt_vervestacks_BIH_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18FA6956-6156-4F40-8A23-665595C55A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{46C2C6F7-EE88-41DE-9BFF-4FC023056781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E7FC8FB8-28F0-4F2F-B40A-50CE7CF82A20}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E7DBE5CF-CC4D-42C6-A6D0-D63487BCD287}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="248">
   <si>
     <t>~fi_t</t>
   </si>
@@ -107,7 +107,7 @@
     <t>coal</t>
   </si>
   <si>
-    <t>e_Zenica_BIH,h_Zenica_BIH</t>
+    <t>e_Sarajevo_BIH,h_Sarajevo_BIH</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000105454-CHP</t>
@@ -167,7 +167,7 @@
     <t>ep_hydro_dam_G100000600193</t>
   </si>
   <si>
-    <t>e_Zenica_BIH</t>
+    <t>e_Travnik_BIH</t>
   </si>
   <si>
     <t>ep_hydro_dam_G100000600196</t>
@@ -473,6 +473,9 @@
     <t>gas</t>
   </si>
   <si>
+    <t>e_Sarajevo_BIH</t>
+  </si>
+  <si>
     <t>en_a_gas_steam_turbine_G100001055253</t>
   </si>
   <si>
@@ -713,7 +716,7 @@
     <t>ep_coal_subcritical_G100000105453-CHP_ccs-rf</t>
   </si>
   <si>
-    <t>e_Zenica_BIH,h_Zenica_BIH,CO2Cap</t>
+    <t>e_Sarajevo_BIH,h_Sarajevo_BIH,CO2Cap</t>
   </si>
   <si>
     <t>ep_coal_subcritical_G100000105454-CHP_ccs-rf</t>
@@ -1153,7 +1156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7FD9B3-A91C-4EA8-BDC6-E23EC5A72A44}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75111068-13D9-4A2C-81F4-C1BE9EAB9A69}">
   <dimension ref="B9:V20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1191,13 +1194,13 @@
         <v>10</v>
       </c>
       <c r="J10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M10" t="s">
         <v>13</v>
@@ -1229,7 +1232,7 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
@@ -1238,7 +1241,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F11">
         <v>9.3936000000000006E-2</v>
@@ -1268,13 +1271,13 @@
         <v>104</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q11" t="s">
         <v>16</v>
       </c>
       <c r="R11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="S11" t="s">
         <v>100</v>
@@ -1291,7 +1294,7 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
@@ -1300,7 +1303,7 @@
         <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F12">
         <v>0.133488</v>
@@ -1330,13 +1333,13 @@
         <v>104</v>
       </c>
       <c r="P12" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q12" t="s">
         <v>16</v>
       </c>
       <c r="R12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="S12" t="s">
         <v>100</v>
@@ -1353,7 +1356,7 @@
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -1362,7 +1365,7 @@
         <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F13">
         <v>0.13765950000000002</v>
@@ -1392,13 +1395,13 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q13" t="s">
         <v>16</v>
       </c>
       <c r="R13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="S13" t="s">
         <v>100</v>
@@ -1415,7 +1418,7 @@
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -1424,7 +1427,7 @@
         <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F14">
         <v>0.17299880000000001</v>
@@ -1454,13 +1457,13 @@
         <v>98</v>
       </c>
       <c r="P14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q14" t="s">
         <v>16</v>
       </c>
       <c r="R14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="S14" t="s">
         <v>100</v>
@@ -1477,7 +1480,7 @@
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -1486,7 +1489,7 @@
         <v>20</v>
       </c>
       <c r="E15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F15">
         <v>0.13348799999999997</v>
@@ -1516,13 +1519,13 @@
         <v>104</v>
       </c>
       <c r="P15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q15" t="s">
         <v>16</v>
       </c>
       <c r="R15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="S15" t="s">
         <v>100</v>
@@ -1539,7 +1542,7 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -1548,7 +1551,7 @@
         <v>20</v>
       </c>
       <c r="E16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F16">
         <v>0.133488</v>
@@ -1578,13 +1581,13 @@
         <v>104</v>
       </c>
       <c r="P16" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q16" t="s">
         <v>16</v>
       </c>
       <c r="R16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="S16" t="s">
         <v>100</v>
@@ -1601,7 +1604,7 @@
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -1610,7 +1613,7 @@
         <v>20</v>
       </c>
       <c r="E17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F17">
         <v>0.133488</v>
@@ -1640,13 +1643,13 @@
         <v>104</v>
       </c>
       <c r="P17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q17" t="s">
         <v>16</v>
       </c>
       <c r="R17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="S17" t="s">
         <v>100</v>
@@ -1663,7 +1666,7 @@
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C18" t="s">
         <v>16</v>
@@ -1672,7 +1675,7 @@
         <v>20</v>
       </c>
       <c r="E18" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F18">
         <v>0.178087</v>
@@ -1702,13 +1705,13 @@
         <v>98</v>
       </c>
       <c r="P18" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q18" t="s">
         <v>16</v>
       </c>
       <c r="R18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S18" t="s">
         <v>100</v>
@@ -1725,7 +1728,7 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
@@ -1734,7 +1737,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F19">
         <v>0.178087</v>
@@ -1764,13 +1767,13 @@
         <v>98</v>
       </c>
       <c r="P19" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q19" t="s">
         <v>16</v>
       </c>
       <c r="R19" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S19" t="s">
         <v>100</v>
@@ -1787,7 +1790,7 @@
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
@@ -1796,7 +1799,7 @@
         <v>20</v>
       </c>
       <c r="E20" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F20">
         <v>9.3936000000000006E-2</v>
@@ -1826,13 +1829,13 @@
         <v>104</v>
       </c>
       <c r="P20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q20" t="s">
         <v>16</v>
       </c>
       <c r="R20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S20" t="s">
         <v>100</v>
@@ -1853,7 +1856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA91237-548F-4D5F-8F7B-9AB320191CB6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91B6F067-78BB-4C49-AD08-6CCDA4243EC6}">
   <dimension ref="B9:X58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1944,7 +1947,7 @@
         <v>142</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="F11">
         <v>2025</v>
@@ -1977,7 +1980,7 @@
         <v>16</v>
       </c>
       <c r="T11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U11" t="s">
         <v>100</v>
@@ -1994,7 +1997,7 @@
     </row>
     <row r="12" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
         <v>16</v>
@@ -2030,13 +2033,13 @@
         <v>98</v>
       </c>
       <c r="R12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="S12" t="s">
         <v>16</v>
       </c>
       <c r="T12" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="U12" t="s">
         <v>100</v>
@@ -2053,7 +2056,7 @@
     </row>
     <row r="13" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" t="s">
         <v>16</v>
@@ -2089,13 +2092,13 @@
         <v>98</v>
       </c>
       <c r="R13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="S13" t="s">
         <v>16</v>
       </c>
       <c r="T13" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="U13" t="s">
         <v>100</v>
@@ -2112,7 +2115,7 @@
     </row>
     <row r="14" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" t="s">
         <v>16</v>
@@ -2148,13 +2151,13 @@
         <v>98</v>
       </c>
       <c r="R14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="S14" t="s">
         <v>16</v>
       </c>
       <c r="T14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U14" t="s">
         <v>100</v>
@@ -2171,7 +2174,7 @@
     </row>
     <row r="15" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C15" t="s">
         <v>16</v>
@@ -2210,13 +2213,13 @@
         <v>98</v>
       </c>
       <c r="R15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="S15" t="s">
         <v>16</v>
       </c>
       <c r="T15" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U15" t="s">
         <v>100</v>
@@ -2233,7 +2236,7 @@
     </row>
     <row r="16" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C16" t="s">
         <v>16</v>
@@ -2242,7 +2245,7 @@
         <v>61</v>
       </c>
       <c r="E16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F16">
         <v>2025</v>
@@ -2272,13 +2275,13 @@
         <v>98</v>
       </c>
       <c r="R16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="S16" t="s">
         <v>16</v>
       </c>
       <c r="T16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U16" t="s">
         <v>100</v>
@@ -2295,7 +2298,7 @@
     </row>
     <row r="17" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -2334,13 +2337,13 @@
         <v>98</v>
       </c>
       <c r="R17" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="S17" t="s">
         <v>16</v>
       </c>
       <c r="T17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U17" t="s">
         <v>100</v>
@@ -2357,7 +2360,7 @@
     </row>
     <row r="18" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C18" t="s">
         <v>16</v>
@@ -2396,13 +2399,13 @@
         <v>98</v>
       </c>
       <c r="R18" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="S18" t="s">
         <v>16</v>
       </c>
       <c r="T18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="U18" t="s">
         <v>100</v>
@@ -2419,7 +2422,7 @@
     </row>
     <row r="19" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" t="s">
         <v>16</v>
@@ -2458,13 +2461,13 @@
         <v>98</v>
       </c>
       <c r="R19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="S19" t="s">
         <v>16</v>
       </c>
       <c r="T19" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="U19" t="s">
         <v>100</v>
@@ -2481,7 +2484,7 @@
     </row>
     <row r="20" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
         <v>16</v>
@@ -2520,13 +2523,13 @@
         <v>98</v>
       </c>
       <c r="R20" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="S20" t="s">
         <v>16</v>
       </c>
       <c r="T20" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="U20" t="s">
         <v>100</v>
@@ -2543,7 +2546,7 @@
     </row>
     <row r="21" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" t="s">
         <v>16</v>
@@ -2579,13 +2582,13 @@
         <v>98</v>
       </c>
       <c r="R21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S21" t="s">
         <v>16</v>
       </c>
       <c r="T21" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="U21" t="s">
         <v>100</v>
@@ -2602,7 +2605,7 @@
     </row>
     <row r="22" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" t="s">
         <v>16</v>
@@ -2638,13 +2641,13 @@
         <v>98</v>
       </c>
       <c r="R22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="S22" t="s">
         <v>16</v>
       </c>
       <c r="T22" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U22" t="s">
         <v>100</v>
@@ -2661,7 +2664,7 @@
     </row>
     <row r="23" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" t="s">
         <v>16</v>
@@ -2697,13 +2700,13 @@
         <v>98</v>
       </c>
       <c r="R23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S23" t="s">
         <v>16</v>
       </c>
       <c r="T23" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="U23" t="s">
         <v>100</v>
@@ -2720,7 +2723,7 @@
     </row>
     <row r="24" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -2756,13 +2759,13 @@
         <v>98</v>
       </c>
       <c r="R24" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S24" t="s">
         <v>16</v>
       </c>
       <c r="T24" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U24" t="s">
         <v>100</v>
@@ -2779,7 +2782,7 @@
     </row>
     <row r="25" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C25" t="s">
         <v>16</v>
@@ -2815,13 +2818,13 @@
         <v>98</v>
       </c>
       <c r="R25" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="S25" t="s">
         <v>16</v>
       </c>
       <c r="T25" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="U25" t="s">
         <v>100</v>
@@ -2838,7 +2841,7 @@
     </row>
     <row r="26" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" t="s">
         <v>16</v>
@@ -2874,13 +2877,13 @@
         <v>98</v>
       </c>
       <c r="R26" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S26" t="s">
         <v>16</v>
       </c>
       <c r="T26" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U26" t="s">
         <v>100</v>
@@ -2897,7 +2900,7 @@
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
         <v>16</v>
@@ -2933,13 +2936,13 @@
         <v>98</v>
       </c>
       <c r="R27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S27" t="s">
         <v>16</v>
       </c>
       <c r="T27" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="U27" t="s">
         <v>100</v>
@@ -2956,7 +2959,7 @@
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C28" t="s">
         <v>16</v>
@@ -2992,13 +2995,13 @@
         <v>98</v>
       </c>
       <c r="R28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="S28" t="s">
         <v>16</v>
       </c>
       <c r="T28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="U28" t="s">
         <v>100</v>
@@ -3015,7 +3018,7 @@
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C29" t="s">
         <v>16</v>
@@ -3051,13 +3054,13 @@
         <v>98</v>
       </c>
       <c r="R29" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="S29" t="s">
         <v>16</v>
       </c>
       <c r="T29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="U29" t="s">
         <v>100</v>
@@ -3074,7 +3077,7 @@
     </row>
     <row r="30" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C30" t="s">
         <v>16</v>
@@ -3110,13 +3113,13 @@
         <v>98</v>
       </c>
       <c r="R30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="S30" t="s">
         <v>16</v>
       </c>
       <c r="T30" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U30" t="s">
         <v>100</v>
@@ -3133,7 +3136,7 @@
     </row>
     <row r="31" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" t="s">
         <v>16</v>
@@ -3169,13 +3172,13 @@
         <v>98</v>
       </c>
       <c r="R31" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="S31" t="s">
         <v>16</v>
       </c>
       <c r="T31" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="U31" t="s">
         <v>100</v>
@@ -3192,7 +3195,7 @@
     </row>
     <row r="32" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C32" t="s">
         <v>16</v>
@@ -3228,13 +3231,13 @@
         <v>98</v>
       </c>
       <c r="R32" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="S32" t="s">
         <v>16</v>
       </c>
       <c r="T32" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="U32" t="s">
         <v>100</v>
@@ -3251,7 +3254,7 @@
     </row>
     <row r="33" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
         <v>16</v>
@@ -3287,13 +3290,13 @@
         <v>98</v>
       </c>
       <c r="R33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="S33" t="s">
         <v>16</v>
       </c>
       <c r="T33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="U33" t="s">
         <v>100</v>
@@ -3310,7 +3313,7 @@
     </row>
     <row r="34" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C34" t="s">
         <v>16</v>
@@ -3346,13 +3349,13 @@
         <v>98</v>
       </c>
       <c r="R34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S34" t="s">
         <v>16</v>
       </c>
       <c r="T34" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U34" t="s">
         <v>100</v>
@@ -3369,7 +3372,7 @@
     </row>
     <row r="35" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C35" t="s">
         <v>16</v>
@@ -3405,13 +3408,13 @@
         <v>98</v>
       </c>
       <c r="R35" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="S35" t="s">
         <v>16</v>
       </c>
       <c r="T35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U35" t="s">
         <v>100</v>
@@ -3428,7 +3431,7 @@
     </row>
     <row r="36" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C36" t="s">
         <v>16</v>
@@ -3467,13 +3470,13 @@
         <v>98</v>
       </c>
       <c r="R36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="S36" t="s">
         <v>16</v>
       </c>
       <c r="T36" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U36" t="s">
         <v>100</v>
@@ -3490,7 +3493,7 @@
     </row>
     <row r="37" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
         <v>16</v>
@@ -3529,13 +3532,13 @@
         <v>98</v>
       </c>
       <c r="R37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="S37" t="s">
         <v>16</v>
       </c>
       <c r="T37" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U37" t="s">
         <v>100</v>
@@ -3552,7 +3555,7 @@
     </row>
     <row r="38" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
         <v>16</v>
@@ -3591,13 +3594,13 @@
         <v>98</v>
       </c>
       <c r="R38" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="S38" t="s">
         <v>16</v>
       </c>
       <c r="T38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U38" t="s">
         <v>100</v>
@@ -3614,7 +3617,7 @@
     </row>
     <row r="39" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C39" t="s">
         <v>16</v>
@@ -3653,13 +3656,13 @@
         <v>98</v>
       </c>
       <c r="R39" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="S39" t="s">
         <v>16</v>
       </c>
       <c r="T39" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U39" t="s">
         <v>100</v>
@@ -3676,7 +3679,7 @@
     </row>
     <row r="40" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C40" t="s">
         <v>16</v>
@@ -3715,13 +3718,13 @@
         <v>98</v>
       </c>
       <c r="R40" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="S40" t="s">
         <v>16</v>
       </c>
       <c r="T40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U40" t="s">
         <v>100</v>
@@ -3738,7 +3741,7 @@
     </row>
     <row r="41" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C41" t="s">
         <v>16</v>
@@ -3777,13 +3780,13 @@
         <v>98</v>
       </c>
       <c r="R41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="S41" t="s">
         <v>16</v>
       </c>
       <c r="T41" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="U41" t="s">
         <v>100</v>
@@ -3800,7 +3803,7 @@
     </row>
     <row r="42" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C42" t="s">
         <v>16</v>
@@ -3839,13 +3842,13 @@
         <v>98</v>
       </c>
       <c r="R42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="S42" t="s">
         <v>16</v>
       </c>
       <c r="T42" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U42" t="s">
         <v>100</v>
@@ -3862,7 +3865,7 @@
     </row>
     <row r="43" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C43" t="s">
         <v>16</v>
@@ -3901,13 +3904,13 @@
         <v>98</v>
       </c>
       <c r="R43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S43" t="s">
         <v>16</v>
       </c>
       <c r="T43" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U43" t="s">
         <v>100</v>
@@ -3924,7 +3927,7 @@
     </row>
     <row r="44" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C44" t="s">
         <v>16</v>
@@ -3963,13 +3966,13 @@
         <v>98</v>
       </c>
       <c r="R44" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="S44" t="s">
         <v>16</v>
       </c>
       <c r="T44" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U44" t="s">
         <v>100</v>
@@ -3986,7 +3989,7 @@
     </row>
     <row r="45" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C45" t="s">
         <v>16</v>
@@ -4025,13 +4028,13 @@
         <v>98</v>
       </c>
       <c r="R45" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="S45" t="s">
         <v>16</v>
       </c>
       <c r="T45" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="U45" t="s">
         <v>100</v>
@@ -4048,7 +4051,7 @@
     </row>
     <row r="46" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C46" t="s">
         <v>16</v>
@@ -4057,7 +4060,7 @@
         <v>83</v>
       </c>
       <c r="E46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F46">
         <v>2025</v>
@@ -4087,13 +4090,13 @@
         <v>98</v>
       </c>
       <c r="R46" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S46" t="s">
         <v>16</v>
       </c>
       <c r="T46" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="U46" t="s">
         <v>100</v>
@@ -4110,7 +4113,7 @@
     </row>
     <row r="47" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C47" t="s">
         <v>16</v>
@@ -4149,13 +4152,13 @@
         <v>98</v>
       </c>
       <c r="R47" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="S47" t="s">
         <v>16</v>
       </c>
       <c r="T47" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="U47" t="s">
         <v>100</v>
@@ -4172,7 +4175,7 @@
     </row>
     <row r="48" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C48" t="s">
         <v>16</v>
@@ -4181,7 +4184,7 @@
         <v>83</v>
       </c>
       <c r="E48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48">
         <v>2025</v>
@@ -4211,13 +4214,13 @@
         <v>98</v>
       </c>
       <c r="R48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="S48" t="s">
         <v>16</v>
       </c>
       <c r="T48" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="U48" t="s">
         <v>100</v>
@@ -4234,7 +4237,7 @@
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C49" t="s">
         <v>16</v>
@@ -4273,13 +4276,13 @@
         <v>130</v>
       </c>
       <c r="R49" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="S49" t="s">
         <v>16</v>
       </c>
       <c r="T49" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U49" t="s">
         <v>100</v>
@@ -4296,7 +4299,7 @@
     </row>
     <row r="50" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C50" t="s">
         <v>16</v>
@@ -4335,13 +4338,13 @@
         <v>130</v>
       </c>
       <c r="R50" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="S50" t="s">
         <v>16</v>
       </c>
       <c r="T50" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="U50" t="s">
         <v>100</v>
@@ -4358,7 +4361,7 @@
     </row>
     <row r="51" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
         <v>16</v>
@@ -4397,13 +4400,13 @@
         <v>98</v>
       </c>
       <c r="R51" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S51" t="s">
         <v>16</v>
       </c>
       <c r="T51" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="U51" t="s">
         <v>100</v>
@@ -4420,7 +4423,7 @@
     </row>
     <row r="52" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C52" t="s">
         <v>16</v>
@@ -4459,13 +4462,13 @@
         <v>98</v>
       </c>
       <c r="R52" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="S52" t="s">
         <v>16</v>
       </c>
       <c r="T52" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="U52" t="s">
         <v>100</v>
@@ -4482,7 +4485,7 @@
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C53" t="s">
         <v>16</v>
@@ -4520,7 +4523,7 @@
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C54" t="s">
         <v>16</v>
@@ -4555,7 +4558,7 @@
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C55" t="s">
         <v>16</v>
@@ -4587,7 +4590,7 @@
     </row>
     <row r="56" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C56" t="s">
         <v>16</v>
@@ -4619,7 +4622,7 @@
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C57" t="s">
         <v>16</v>
@@ -4654,7 +4657,7 @@
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C58" t="s">
         <v>16</v>
@@ -4693,7 +4696,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC929CE-9558-4E70-A94D-ACD8A88CC12F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612777B3-A16F-40E0-AC35-99E1FA057C87}">
   <dimension ref="B9:X75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6637,7 +6640,7 @@
         <v>33</v>
       </c>
       <c r="O42">
-        <v>0.18526537357485859</v>
+        <v>0.18526537357485862</v>
       </c>
       <c r="Q42" t="s">
         <v>98</v>
@@ -6690,7 +6693,7 @@
         <v>33</v>
       </c>
       <c r="O43">
-        <v>0.18526537357485859</v>
+        <v>0.18526537357485862</v>
       </c>
       <c r="Q43" t="s">
         <v>98</v>
@@ -6743,7 +6746,7 @@
         <v>33</v>
       </c>
       <c r="O44">
-        <v>0.18526537357485859</v>
+        <v>0.18526537357485862</v>
       </c>
       <c r="Q44" t="s">
         <v>98</v>
@@ -6879,7 +6882,7 @@
         <v>16</v>
       </c>
       <c r="T46" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="U46" t="s">
         <v>100</v>
@@ -6941,7 +6944,7 @@
         <v>16</v>
       </c>
       <c r="T47" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="U47" t="s">
         <v>100</v>
@@ -7003,7 +7006,7 @@
         <v>16</v>
       </c>
       <c r="T48" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="U48" t="s">
         <v>100</v>
@@ -7065,7 +7068,7 @@
         <v>16</v>
       </c>
       <c r="T49" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="U49" t="s">
         <v>100</v>
@@ -7623,7 +7626,7 @@
         <v>16</v>
       </c>
       <c r="T58" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="U58" t="s">
         <v>100</v>
@@ -7685,7 +7688,7 @@
         <v>16</v>
       </c>
       <c r="T59" t="s">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="U59" t="s">
         <v>100</v>
@@ -8314,7 +8317,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B682F8D6-8386-4F94-9E14-DDB38A50BD7C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EC99030-C224-43E5-A0E9-CAB95E2ADF4E}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
